--- a/assets/reference/产品宽度--原始数据 -模板.xlsx
+++ b/assets/reference/产品宽度--原始数据 -模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7000"/>
+    <workbookView windowWidth="21940" windowHeight="12400" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="规上用户-产品宽度" sheetId="3" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="93">
   <si>
     <t>最终用户-行业</t>
   </si>
@@ -306,6 +306,15 @@
   </si>
   <si>
     <t>A/B/C</t>
+  </si>
+  <si>
+    <t>1-1GXJNSSX</t>
+  </si>
+  <si>
+    <t>立讯精XXX业股份有限公司</t>
+  </si>
+  <si>
+    <t>张岩</t>
   </si>
 </sst>
 </file>
@@ -1002,10 +1011,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1469,113 +1478,113 @@
       </c>
     </row>
     <row r="2" spans="1:36">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="6">
         <f t="shared" ref="G2:G13" si="0">SUM(H2:AH2)</f>
         <v>25</v>
       </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1</v>
-      </c>
-      <c r="K2" s="6">
-        <v>1</v>
-      </c>
-      <c r="L2" s="6">
-        <v>1</v>
-      </c>
-      <c r="M2" s="6">
-        <v>1</v>
-      </c>
-      <c r="N2" s="6">
-        <v>1</v>
-      </c>
-      <c r="O2" s="6">
-        <v>1</v>
-      </c>
-      <c r="P2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>1</v>
-      </c>
-      <c r="R2" s="6">
-        <v>1</v>
-      </c>
-      <c r="S2" s="6">
-        <v>1</v>
-      </c>
-      <c r="T2" s="6">
-        <v>1</v>
-      </c>
-      <c r="U2" s="6">
-        <v>1</v>
-      </c>
-      <c r="V2" s="6">
-        <v>1</v>
-      </c>
-      <c r="W2" s="6">
-        <v>1</v>
-      </c>
-      <c r="X2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="6" t="s">
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5">
+        <v>1</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>1</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>1</v>
+      </c>
+      <c r="S2" s="5">
+        <v>1</v>
+      </c>
+      <c r="T2" s="5">
+        <v>1</v>
+      </c>
+      <c r="U2" s="5">
+        <v>1</v>
+      </c>
+      <c r="V2" s="5">
+        <v>1</v>
+      </c>
+      <c r="W2" s="5">
+        <v>1</v>
+      </c>
+      <c r="X2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AJ2" s="6" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -1595,7 +1604,7 @@
       <c r="E3" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G3" s="9">
@@ -1691,113 +1700,113 @@
       </c>
     </row>
     <row r="4" spans="1:36">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="6">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="H4" s="6">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6">
-        <v>1</v>
-      </c>
-      <c r="J4" s="6">
-        <v>1</v>
-      </c>
-      <c r="K4" s="6">
-        <v>1</v>
-      </c>
-      <c r="L4" s="6">
-        <v>1</v>
-      </c>
-      <c r="M4" s="6">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6">
-        <v>1</v>
-      </c>
-      <c r="O4" s="6">
-        <v>1</v>
-      </c>
-      <c r="P4" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="6">
-        <v>1</v>
-      </c>
-      <c r="R4" s="6">
-        <v>0</v>
-      </c>
-      <c r="S4" s="6">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6">
-        <v>1</v>
-      </c>
-      <c r="U4" s="6">
-        <v>1</v>
-      </c>
-      <c r="V4" s="6">
-        <v>1</v>
-      </c>
-      <c r="W4" s="6">
-        <v>1</v>
-      </c>
-      <c r="X4" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI4" s="6" t="s">
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+      <c r="O4" s="5">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
+      <c r="U4" s="5">
+        <v>1</v>
+      </c>
+      <c r="V4" s="5">
+        <v>1</v>
+      </c>
+      <c r="W4" s="5">
+        <v>1</v>
+      </c>
+      <c r="X4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AJ4" s="6" t="s">
+      <c r="AJ4" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -1817,7 +1826,7 @@
       <c r="E5" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G5" s="9">
@@ -1908,115 +1917,115 @@
       <c r="AI5" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AJ5" s="6" t="s">
+      <c r="AJ5" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:36">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="6">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="6">
-        <v>1</v>
-      </c>
-      <c r="L6" s="6">
-        <v>1</v>
-      </c>
-      <c r="M6" s="6">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6">
-        <v>1</v>
-      </c>
-      <c r="O6" s="6">
-        <v>1</v>
-      </c>
-      <c r="P6" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>1</v>
-      </c>
-      <c r="R6" s="6">
-        <v>1</v>
-      </c>
-      <c r="S6" s="6">
-        <v>0</v>
-      </c>
-      <c r="T6" s="6">
-        <v>1</v>
-      </c>
-      <c r="U6" s="6">
-        <v>1</v>
-      </c>
-      <c r="V6" s="6">
-        <v>1</v>
-      </c>
-      <c r="W6" s="6">
-        <v>1</v>
-      </c>
-      <c r="X6" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="6" t="s">
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+      <c r="L6" s="5">
+        <v>1</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>1</v>
+      </c>
+      <c r="O6" s="5">
+        <v>1</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5">
+        <v>1</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5">
+        <v>1</v>
+      </c>
+      <c r="V6" s="5">
+        <v>1</v>
+      </c>
+      <c r="W6" s="5">
+        <v>1</v>
+      </c>
+      <c r="X6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="5" t="s">
         <v>42</v>
       </c>
       <c r="AJ6" s="8" t="s">
@@ -2039,7 +2048,7 @@
       <c r="E7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="9">
@@ -2130,118 +2139,118 @@
       <c r="AI7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AJ7" s="6" t="s">
+      <c r="AJ7" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:36">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>0</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6">
-        <v>0</v>
-      </c>
-      <c r="M8" s="6">
-        <v>0</v>
-      </c>
-      <c r="N8" s="6">
-        <v>1</v>
-      </c>
-      <c r="O8" s="6">
-        <v>0</v>
-      </c>
-      <c r="P8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>0</v>
-      </c>
-      <c r="R8" s="6">
-        <v>0</v>
-      </c>
-      <c r="S8" s="6">
-        <v>0</v>
-      </c>
-      <c r="T8" s="6">
-        <v>0</v>
-      </c>
-      <c r="U8" s="6">
-        <v>0</v>
-      </c>
-      <c r="V8" s="6">
-        <v>0</v>
-      </c>
-      <c r="W8" s="6">
-        <v>0</v>
-      </c>
-      <c r="X8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="6" t="s">
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>1</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AJ8" s="6" t="s">
+      <c r="AJ8" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2261,7 +2270,7 @@
       <c r="E9" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G9" s="9">
@@ -2357,113 +2366,113 @@
       </c>
     </row>
     <row r="10" spans="1:36">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6">
-        <v>1</v>
-      </c>
-      <c r="M10" s="6">
-        <v>0</v>
-      </c>
-      <c r="N10" s="6">
-        <v>1</v>
-      </c>
-      <c r="O10" s="6">
-        <v>0</v>
-      </c>
-      <c r="P10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>0</v>
-      </c>
-      <c r="R10" s="6">
-        <v>0</v>
-      </c>
-      <c r="S10" s="6">
-        <v>1</v>
-      </c>
-      <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="6">
-        <v>0</v>
-      </c>
-      <c r="V10" s="6">
-        <v>0</v>
-      </c>
-      <c r="W10" s="6">
-        <v>0</v>
-      </c>
-      <c r="X10" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI10" s="6" t="s">
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+      <c r="O10" s="5">
+        <v>0</v>
+      </c>
+      <c r="P10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
+      <c r="R10" s="5">
+        <v>0</v>
+      </c>
+      <c r="S10" s="5">
+        <v>1</v>
+      </c>
+      <c r="T10" s="5">
+        <v>0</v>
+      </c>
+      <c r="U10" s="5">
+        <v>0</v>
+      </c>
+      <c r="V10" s="5">
+        <v>0</v>
+      </c>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
+      <c r="X10" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="5">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
+        <v>1</v>
+      </c>
+      <c r="AI10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="6" t="s">
+      <c r="AJ10" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2483,7 +2492,7 @@
       <c r="E11" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>41</v>
       </c>
       <c r="G11" s="9">
@@ -2574,115 +2583,115 @@
       <c r="AI11" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AJ11" s="6" t="s">
+      <c r="AJ11" s="5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:36">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6">
-        <v>1</v>
-      </c>
-      <c r="J12" s="6">
-        <v>0</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6">
-        <v>0</v>
-      </c>
-      <c r="M12" s="6">
-        <v>0</v>
-      </c>
-      <c r="N12" s="6">
-        <v>1</v>
-      </c>
-      <c r="O12" s="6">
-        <v>0</v>
-      </c>
-      <c r="P12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="6">
-        <v>0</v>
-      </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6">
-        <v>0</v>
-      </c>
-      <c r="W12" s="6">
-        <v>0</v>
-      </c>
-      <c r="X12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="6">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="6" t="s">
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+      <c r="O12" s="5">
+        <v>0</v>
+      </c>
+      <c r="P12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
+      <c r="R12" s="5">
+        <v>0</v>
+      </c>
+      <c r="S12" s="5">
+        <v>0</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="5">
+        <v>0</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="X12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="5" t="s">
         <v>42</v>
       </c>
       <c r="AJ12" s="8" t="s">
@@ -2796,7 +2805,7 @@
       <c r="AI13" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AJ13" s="6" t="s">
+      <c r="AJ13" s="5" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2822,8 +2831,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AI2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
+  <dimension ref="A1:AI3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="12.5416666666667" customWidth="1"/>
     <col min="2" max="2" width="21.175" customWidth="1"/>
@@ -2951,90 +2960,92 @@
       <c r="D2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5">
-        <f t="shared" ref="F2" si="0">SUM(G2:AG2)</f>
+      <c r="E2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F2" s="6">
+        <f t="shared" ref="F2:F3" si="0">SUM(G2:AG2)</f>
         <v>25</v>
       </c>
-      <c r="G2" s="6">
-        <v>1</v>
-      </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6">
-        <v>1</v>
-      </c>
-      <c r="J2" s="6">
-        <v>1</v>
-      </c>
-      <c r="K2" s="6">
-        <v>1</v>
-      </c>
-      <c r="L2" s="6">
-        <v>1</v>
-      </c>
-      <c r="M2" s="6">
-        <v>1</v>
-      </c>
-      <c r="N2" s="6">
-        <v>1</v>
-      </c>
-      <c r="O2" s="6">
-        <v>1</v>
-      </c>
-      <c r="P2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="6">
-        <v>1</v>
-      </c>
-      <c r="R2" s="6">
-        <v>1</v>
-      </c>
-      <c r="S2" s="6">
-        <v>1</v>
-      </c>
-      <c r="T2" s="6">
-        <v>1</v>
-      </c>
-      <c r="U2" s="6">
-        <v>1</v>
-      </c>
-      <c r="V2" s="6">
-        <v>1</v>
-      </c>
-      <c r="W2" s="6">
-        <v>1</v>
-      </c>
-      <c r="X2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="6">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="6">
+      <c r="G2" s="5">
+        <v>1</v>
+      </c>
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="5">
+        <v>1</v>
+      </c>
+      <c r="L2" s="5">
+        <v>1</v>
+      </c>
+      <c r="M2" s="5">
+        <v>1</v>
+      </c>
+      <c r="N2" s="5">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="5">
+        <v>1</v>
+      </c>
+      <c r="R2" s="5">
+        <v>1</v>
+      </c>
+      <c r="S2" s="5">
+        <v>1</v>
+      </c>
+      <c r="T2" s="5">
+        <v>1</v>
+      </c>
+      <c r="U2" s="5">
+        <v>1</v>
+      </c>
+      <c r="V2" s="5">
+        <v>1</v>
+      </c>
+      <c r="W2" s="5">
+        <v>1</v>
+      </c>
+      <c r="X2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="5">
         <v>1</v>
       </c>
       <c r="AH2" s="4" t="s">
@@ -3044,9 +3055,122 @@
         <v>89</v>
       </c>
     </row>
+    <row r="3" ht="23" customHeight="1" spans="1:35">
+      <c r="A3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" s="6">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>0</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+      <c r="T3" s="5">
+        <v>1</v>
+      </c>
+      <c r="U3" s="5">
+        <v>1</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1</v>
+      </c>
+      <c r="W3" s="5">
+        <v>1</v>
+      </c>
+      <c r="X3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="G3:AG3">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G1:AG2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
